--- a/backend/data/financials_by_company/0082.HK.xlsx
+++ b/backend/data/financials_by_company/0082.HK.xlsx
@@ -4446,7 +4446,7 @@
         <v>-4868000</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
         <v>0.09</v>
@@ -4694,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
         <v>0.09</v>
